--- a/cleaning_forms/023_railcar_cleaning_inspection_checklist--cleaning_forms.xlsx
+++ b/cleaning_forms/023_railcar_cleaning_inspection_checklist--cleaning_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -895,8 +895,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="35" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -924,12 +924,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'team_a'}</t>
+          <t>team_a</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Team A'}</t>
+          <t>Team A</t>
         </is>
       </c>
     </row>
@@ -941,12 +941,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'team_b'}</t>
+          <t>team_b</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Team B'}</t>
+          <t>Team B</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'team_c'}</t>
+          <t>team_c</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Team C'}</t>
+          <t>Team C</t>
         </is>
       </c>
     </row>
@@ -975,12 +975,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'railcar_1'}</t>
+          <t>railcar_1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Railcar 1'}</t>
+          <t>Railcar 1</t>
         </is>
       </c>
     </row>
@@ -992,12 +992,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'railcar_2'}</t>
+          <t>railcar_2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Railcar 2'}</t>
+          <t>Railcar 2</t>
         </is>
       </c>
     </row>
@@ -1009,12 +1009,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'railcar_3'}</t>
+          <t>railcar_3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Railcar 3'}</t>
+          <t>Railcar 3</t>
         </is>
       </c>
     </row>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'method_1'}</t>
+          <t>method_1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Method 1'}</t>
+          <t>Method 1</t>
         </is>
       </c>
     </row>
@@ -1043,12 +1043,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'method_2'}</t>
+          <t>method_2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Method 2'}</t>
+          <t>Method 2</t>
         </is>
       </c>
     </row>
@@ -1060,12 +1060,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'method_3'}</t>
+          <t>method_3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Method 3'}</t>
+          <t>Method 3</t>
         </is>
       </c>
     </row>
@@ -1077,12 +1077,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1094,12 +1094,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1111,12 +1111,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -1128,12 +1128,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Daily'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -1145,12 +1145,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'weekly'}</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Weekly'}</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
@@ -1162,12 +1162,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'monthly'}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Monthly'}</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
@@ -1179,12 +1179,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'jimmy'}</t>
+          <t>jimmy</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Jimmy'}</t>
+          <t>Jimmy</t>
         </is>
       </c>
     </row>
@@ -1196,12 +1196,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'john'}</t>
+          <t>john</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'John'}</t>
+          <t>John</t>
         </is>
       </c>
     </row>
@@ -1213,12 +1213,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'jane'}</t>
+          <t>jane</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Jane'}</t>
+          <t>Jane</t>
         </is>
       </c>
     </row>
@@ -1230,12 +1230,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'soap'}</t>
+          <t>soap</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Soap'}</t>
+          <t>Soap</t>
         </is>
       </c>
     </row>
@@ -1247,12 +1247,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'water'}</t>
+          <t>water</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Water'}</t>
+          <t>Water</t>
         </is>
       </c>
     </row>
@@ -1264,12 +1264,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'rag'}</t>
+          <t>rag</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Rag'}</t>
+          <t>Rag</t>
         </is>
       </c>
     </row>
@@ -1281,12 +1281,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'inactive'}</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Inactive'}</t>
+          <t>Inactive</t>
         </is>
       </c>
     </row>
@@ -1298,12 +1298,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'active'}</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Active'}</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -1315,12 +1315,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'retired'}</t>
+          <t>retired</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Retired'}</t>
+          <t>Retired</t>
         </is>
       </c>
     </row>
@@ -1332,12 +1332,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'location_1'}</t>
+          <t>location_1</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Location 1'}</t>
+          <t>Location 1</t>
         </is>
       </c>
     </row>
@@ -1349,12 +1349,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'location_2'}</t>
+          <t>location_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Location 2'}</t>
+          <t>Location 2</t>
         </is>
       </c>
     </row>
@@ -1366,12 +1366,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'location_3'}</t>
+          <t>location_3</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Location 3'}</t>
+          <t>Location 3</t>
         </is>
       </c>
     </row>
@@ -1383,12 +1383,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1400,12 +1400,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Pending'}</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -1434,12 +1434,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'complete'}</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Complete'}</t>
+          <t>Complete</t>
         </is>
       </c>
     </row>
@@ -1451,12 +1451,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'in_progress'}</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'In Progress'}</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
@@ -1468,12 +1468,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'not_started'}</t>
+          <t>not_started</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Not Started'}</t>
+          <t>Not Started</t>
         </is>
       </c>
     </row>
@@ -1485,12 +1485,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'passed'}</t>
+          <t>passed</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Passed'}</t>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -1502,12 +1502,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'failed'}</t>
+          <t>failed</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Failed'}</t>
+          <t>Failed</t>
         </is>
       </c>
     </row>
@@ -1519,12 +1519,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Pending'}</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
